--- a/data/trans_orig/IP16A09-Clase-trans_orig.xlsx
+++ b/data/trans_orig/IP16A09-Clase-trans_orig.xlsx
@@ -737,7 +737,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>3100</t>
+          <t>3164</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -752,7 +752,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>20,44%</t>
+          <t>20,86%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -772,7 +772,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>4571</t>
+          <t>4683</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -787,7 +787,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>21,3%</t>
+          <t>21,82%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>510</t>
+          <t>642</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>5355</t>
+          <t>5785</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>14,62%</t>
+          <t>15,79%</t>
         </is>
       </c>
     </row>
@@ -845,7 +845,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>12071</t>
+          <t>12007</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -860,7 +860,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>79,56%</t>
+          <t>79,14%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>16891</t>
+          <t>16779</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -895,7 +895,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>78,7%</t>
+          <t>78,18%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>31278</t>
+          <t>30848</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>36123</t>
+          <t>35991</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>85,38%</t>
+          <t>84,21%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,61%</t>
+          <t>98,25%</t>
         </is>
       </c>
     </row>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3097</t>
+          <t>3148</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1095,7 +1095,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>15,94%</t>
+          <t>16,2%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1115,7 +1115,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>3319</t>
+          <t>3521</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1130,7 +1130,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>18,59%</t>
+          <t>19,72%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>4468</t>
+          <t>4097</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>11,98%</t>
+          <t>10,99%</t>
         </is>
       </c>
     </row>
@@ -1188,7 +1188,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>16333</t>
+          <t>16282</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -1203,7 +1203,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>84,06%</t>
+          <t>83,8%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>14538</t>
+          <t>14336</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -1238,7 +1238,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>81,41%</t>
+          <t>80,28%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1258,7 +1258,7 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>32819</t>
+          <t>33190</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
@@ -1273,7 +1273,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>88,02%</t>
+          <t>89,01%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>3680</t>
+          <t>3600</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1438,7 +1438,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>33,12%</t>
+          <t>32,4%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1458,7 +1458,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>3872</t>
+          <t>3255</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1473,7 +1473,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>17,64%</t>
+          <t>14,83%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>515</t>
+          <t>519</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>4956</t>
+          <t>4530</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1503,12 +1503,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>14,99%</t>
+          <t>13,7%</t>
         </is>
       </c>
     </row>
@@ -1531,7 +1531,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>7430</t>
+          <t>7510</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>66,88%</t>
+          <t>67,6%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1566,7 +1566,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>18080</t>
+          <t>18697</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>82,36%</t>
+          <t>85,17%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1601,12 +1601,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>28106</t>
+          <t>28532</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>32547</t>
+          <t>32543</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1616,12 +1616,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>85,01%</t>
+          <t>86,3%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,44%</t>
+          <t>98,43%</t>
         </is>
       </c>
     </row>
@@ -1766,7 +1766,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>3970</t>
+          <t>3946</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>10,53%</t>
+          <t>10,47%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1801,7 +1801,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>3277</t>
+          <t>3263</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>8,45%</t>
+          <t>8,41%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1836,7 +1836,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>4986</t>
+          <t>4403</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,52%</t>
+          <t>5,76%</t>
         </is>
       </c>
     </row>
@@ -1874,7 +1874,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>33715</t>
+          <t>33739</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1889,7 +1889,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>89,47%</t>
+          <t>89,53%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1909,7 +1909,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>35512</t>
+          <t>35526</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -1924,7 +1924,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>91,55%</t>
+          <t>91,59%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -1944,7 +1944,7 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>71489</t>
+          <t>72072</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
@@ -1959,7 +1959,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>93,48%</t>
+          <t>94,24%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -2104,12 +2104,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>505</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>4545</t>
+          <t>4534</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2119,12 +2119,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,68%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>24,11%</t>
+          <t>24,05%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2174,12 +2174,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>512</t>
+          <t>516</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>4089</t>
+          <t>4484</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2189,12 +2189,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>9,56%</t>
+          <t>10,49%</t>
         </is>
       </c>
     </row>
@@ -2217,12 +2217,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>14308</t>
+          <t>14319</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>18354</t>
+          <t>18348</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2232,12 +2232,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>75,89%</t>
+          <t>75,95%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>97,35%</t>
+          <t>97,32%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2287,12 +2287,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>38663</t>
+          <t>38268</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>42240</t>
+          <t>42236</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2302,12 +2302,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>90,44%</t>
+          <t>89,51%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,8%</t>
+          <t>98,79%</t>
         </is>
       </c>
     </row>
@@ -2790,12 +2790,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>2613</t>
+          <t>2596</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>9301</t>
+          <t>9867</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2805,12 +2805,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>8,48%</t>
+          <t>8,99%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2825,12 +2825,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1295</t>
+          <t>1291</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>7564</t>
+          <t>7172</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2840,12 +2840,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>5,59%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2860,12 +2860,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>4775</t>
+          <t>4441</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>13437</t>
+          <t>13527</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2875,12 +2875,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>5,48%</t>
+          <t>5,52%</t>
         </is>
       </c>
     </row>
@@ -2903,12 +2903,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>100433</t>
+          <t>99867</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>107121</t>
+          <t>107138</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2918,12 +2918,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>91,52%</t>
+          <t>91,01%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>97,62%</t>
+          <t>97,63%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2938,12 +2938,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>127733</t>
+          <t>128125</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>134002</t>
+          <t>134006</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2953,12 +2953,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>94,41%</t>
+          <t>94,7%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>99,04%</t>
+          <t>99,05%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2973,12 +2973,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>231593</t>
+          <t>231503</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>240255</t>
+          <t>240589</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2988,12 +2988,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>94,52%</t>
+          <t>94,48%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>98,05%</t>
+          <t>98,19%</t>
         </is>
       </c>
     </row>
@@ -3715,7 +3715,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3198</t>
+          <t>3807</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3730,7 +3730,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>12,48%</t>
+          <t>14,86%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3785,7 +3785,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>4399</t>
+          <t>3873</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3800,7 +3800,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>10,86%</t>
+          <t>9,56%</t>
         </is>
       </c>
     </row>
@@ -3823,7 +3823,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>22421</t>
+          <t>21812</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -3838,7 +3838,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>87,52%</t>
+          <t>85,14%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -3893,7 +3893,7 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>36121</t>
+          <t>36647</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
@@ -3908,7 +3908,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>89,14%</t>
+          <t>90,44%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -4058,7 +4058,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>2619</t>
+          <t>3004</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4073,7 +4073,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>16,41%</t>
+          <t>18,82%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4093,7 +4093,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>4024</t>
+          <t>3661</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4108,7 +4108,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>22,08%</t>
+          <t>20,09%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4128,7 +4128,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>4214</t>
+          <t>4560</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4143,7 +4143,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>12,33%</t>
+          <t>13,34%</t>
         </is>
       </c>
     </row>
@@ -4166,7 +4166,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>13342</t>
+          <t>12957</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -4181,7 +4181,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>83,59%</t>
+          <t>81,18%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -4201,7 +4201,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>14199</t>
+          <t>14562</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -4216,7 +4216,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>77,92%</t>
+          <t>79,91%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -4236,7 +4236,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>29970</t>
+          <t>29624</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -4251,7 +4251,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>87,67%</t>
+          <t>86,66%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -4396,12 +4396,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>513</t>
+          <t>502</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>6022</t>
+          <t>6079</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4411,12 +4411,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>9,96%</t>
+          <t>10,05%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4436,7 +4436,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>5690</t>
+          <t>5658</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4451,7 +4451,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>7,82%</t>
+          <t>7,78%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4466,12 +4466,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1029</t>
+          <t>1201</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>8623</t>
+          <t>8388</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4481,12 +4481,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,47%</t>
+          <t>6,3%</t>
         </is>
       </c>
     </row>
@@ -4509,12 +4509,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>54455</t>
+          <t>54398</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>59964</t>
+          <t>59975</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4524,12 +4524,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>90,04%</t>
+          <t>89,95%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,15%</t>
+          <t>99,17%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4544,7 +4544,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>67063</t>
+          <t>67095</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -4559,7 +4559,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>92,18%</t>
+          <t>92,22%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -4579,12 +4579,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>124608</t>
+          <t>124843</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>132202</t>
+          <t>132030</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4594,12 +4594,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>93,53%</t>
+          <t>93,7%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,23%</t>
+          <t>99,1%</t>
         </is>
       </c>
     </row>
@@ -4779,7 +4779,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>3283</t>
+          <t>2951</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4794,7 +4794,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>9,76%</t>
+          <t>8,78%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4814,7 +4814,7 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>3078</t>
+          <t>3247</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4829,7 +4829,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>4,56%</t>
         </is>
       </c>
     </row>
@@ -4887,7 +4887,7 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>30347</t>
+          <t>30679</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -4902,7 +4902,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>90,24%</t>
+          <t>91,22%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -4922,7 +4922,7 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>68151</t>
+          <t>67982</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
@@ -4937,7 +4937,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>95,68%</t>
+          <t>95,44%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -5117,12 +5117,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>662</t>
+          <t>640</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>5562</t>
+          <t>5432</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5132,12 +5132,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>4,57%</t>
+          <t>4,42%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>38,42%</t>
+          <t>37,52%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5152,12 +5152,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>644</t>
+          <t>729</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>6044</t>
+          <t>6585</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5167,12 +5167,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,78%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>23,0%</t>
+          <t>25,07%</t>
         </is>
       </c>
     </row>
@@ -5230,12 +5230,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>8914</t>
+          <t>9044</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>13814</t>
+          <t>13836</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5245,12 +5245,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>61,58%</t>
+          <t>62,48%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>95,43%</t>
+          <t>95,58%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5265,12 +5265,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>20227</t>
+          <t>19686</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>25627</t>
+          <t>25542</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5280,12 +5280,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>77,0%</t>
+          <t>74,93%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>97,55%</t>
+          <t>97,22%</t>
         </is>
       </c>
     </row>
@@ -5425,12 +5425,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1275</t>
+          <t>1123</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>7897</t>
+          <t>7630</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5440,12 +5440,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>4,28%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5460,12 +5460,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>2631</t>
+          <t>2544</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>10281</t>
+          <t>10814</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5475,12 +5475,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>5,75%</t>
+          <t>6,04%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5495,12 +5495,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>4880</t>
+          <t>4958</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>14808</t>
+          <t>14855</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5510,12 +5510,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>4,16%</t>
         </is>
       </c>
     </row>
@@ -5538,12 +5538,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>170357</t>
+          <t>170624</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>176979</t>
+          <t>177131</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5553,12 +5553,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>95,57%</t>
+          <t>95,72%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>99,28%</t>
+          <t>99,37%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5573,12 +5573,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>168655</t>
+          <t>168122</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>176305</t>
+          <t>176392</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5588,12 +5588,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>94,25%</t>
+          <t>93,96%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>98,53%</t>
+          <t>98,58%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5608,12 +5608,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>342382</t>
+          <t>342335</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>352310</t>
+          <t>352232</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5623,12 +5623,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>95,85%</t>
+          <t>95,84%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>98,63%</t>
+          <t>98,61%</t>
         </is>
       </c>
     </row>
@@ -6350,7 +6350,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3972</t>
+          <t>3528</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6365,7 +6365,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>19,73%</t>
+          <t>17,53%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6385,7 +6385,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>4347</t>
+          <t>4792</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6400,7 +6400,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>19,53%</t>
+          <t>21,53%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6415,12 +6415,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>689</t>
+          <t>701</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>6431</t>
+          <t>5835</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6430,12 +6430,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>15,17%</t>
+          <t>13,77%</t>
         </is>
       </c>
     </row>
@@ -6458,7 +6458,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>16158</t>
+          <t>16602</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -6473,7 +6473,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>80,27%</t>
+          <t>82,47%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -6493,7 +6493,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>17914</t>
+          <t>17469</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -6508,7 +6508,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>80,47%</t>
+          <t>78,47%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -6528,12 +6528,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>35959</t>
+          <t>36555</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>41701</t>
+          <t>41689</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6543,12 +6543,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>84,83%</t>
+          <t>86,23%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,38%</t>
+          <t>98,35%</t>
         </is>
       </c>
     </row>
@@ -6728,7 +6728,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>3683</t>
+          <t>3474</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6743,7 +6743,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>31,27%</t>
+          <t>29,5%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6763,7 +6763,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>3136</t>
+          <t>3540</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6778,7 +6778,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>13,25%</t>
+          <t>14,96%</t>
         </is>
       </c>
     </row>
@@ -6836,7 +6836,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>8095</t>
+          <t>8304</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -6851,7 +6851,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>68,73%</t>
+          <t>70,5%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -6871,7 +6871,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>20525</t>
+          <t>20121</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -6886,7 +6886,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>86,75%</t>
+          <t>85,04%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -7036,7 +7036,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>3932</t>
+          <t>4155</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7051,7 +7051,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,95%</t>
+          <t>7,35%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7071,7 +7071,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>2867</t>
+          <t>3552</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7086,7 +7086,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>6,67%</t>
+          <t>8,26%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7101,12 +7101,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>553</t>
+          <t>552</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>5134</t>
+          <t>4985</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7116,12 +7116,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>5,01%</t>
         </is>
       </c>
     </row>
@@ -7144,7 +7144,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>52629</t>
+          <t>52406</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -7159,7 +7159,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>93,05%</t>
+          <t>92,65%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -7179,7 +7179,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>40130</t>
+          <t>39445</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -7194,7 +7194,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>93,33%</t>
+          <t>91,74%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -7214,12 +7214,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>94424</t>
+          <t>94573</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>99005</t>
+          <t>99006</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7229,12 +7229,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>94,84%</t>
+          <t>94,99%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,44%</t>
+          <t>99,45%</t>
         </is>
       </c>
     </row>
@@ -8060,12 +8060,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>568</t>
+          <t>601</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>5248</t>
+          <t>5367</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8075,12 +8075,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>3,43%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8095,12 +8095,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>698</t>
+          <t>703</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>6394</t>
+          <t>7029</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8115,7 +8115,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>4,55%</t>
+          <t>5,01%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8130,12 +8130,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>2405</t>
+          <t>2463</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>9803</t>
+          <t>9645</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8145,12 +8145,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>3,25%</t>
         </is>
       </c>
     </row>
@@ -8173,12 +8173,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>151129</t>
+          <t>151010</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>155809</t>
+          <t>155776</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8188,12 +8188,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>96,64%</t>
+          <t>96,57%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>99,64%</t>
+          <t>99,62%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8208,12 +8208,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>134000</t>
+          <t>133365</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>139696</t>
+          <t>139691</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8223,7 +8223,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>95,45%</t>
+          <t>94,99%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -8243,12 +8243,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>286967</t>
+          <t>287125</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>294365</t>
+          <t>294307</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8258,12 +8258,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>96,7%</t>
+          <t>96,75%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>99,19%</t>
+          <t>99,17%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP16A09-Clase-trans_orig.xlsx
+++ b/data/trans_orig/IP16A09-Clase-trans_orig.xlsx
@@ -543,7 +543,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -554,7 +554,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -727,67 +727,67 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
+          <t>1333</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>4163</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>6,21%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>19,4%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
           <t>965</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>3164</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>3122</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>6,36%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>20,86%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>1333</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>4683</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>6,21%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>21,82%</t>
+          <t>20,58%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>642</t>
+          <t>641</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>5785</t>
+          <t>5559</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -822,7 +822,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>15,79%</t>
+          <t>15,18%</t>
         </is>
       </c>
     </row>
@@ -835,74 +835,74 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>20129</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>17299</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>21462</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>93,79%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>80,6%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>23</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>14206</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>12007</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>12049</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
         <is>
           <t>15171</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>93,64%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>79,14%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>79,42%</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>20129</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>16779</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>21462</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>93,79%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>78,18%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
           <t>53</t>
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>30848</t>
+          <t>31074</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>35991</t>
+          <t>35992</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,7 +930,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>84,21%</t>
+          <t>84,82%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -948,57 +948,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>21462</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>21462</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>21462</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>25</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>15171</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>15171</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>15171</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>21462</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>21462</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>21462</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1070,102 +1070,102 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
+          <t>647</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>2862</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>3,62%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>16,02%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
           <t>613</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>3148</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>3555</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>3,15%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>16,2%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>647</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>18,29%</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R7" s="2" t="inlineStr">
+        <is>
+          <t>1260</t>
+        </is>
+      </c>
+      <c r="S7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>3521</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>3,62%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>3882</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
+          <t>3,38%</t>
+        </is>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>19,72%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>1260</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>4097</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>3,38%</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>10,99%</t>
+          <t>10,41%</t>
         </is>
       </c>
     </row>
@@ -1178,74 +1178,74 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>17210</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>14995</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>17857</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>96,38%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>83,98%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>28</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>18817</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>16282</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>15875</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
         <is>
           <t>19430</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>96,85%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>83,8%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>81,71%</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>17210</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>14336</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>17857</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>96,38%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>80,28%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
           <t>54</t>
@@ -1258,7 +1258,7 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>33190</t>
+          <t>33405</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
@@ -1273,7 +1273,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>89,01%</t>
+          <t>89,59%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -1291,57 +1291,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>17857</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>17857</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>17857</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>29</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>19430</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>19430</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>19430</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>17857</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>17857</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>17857</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1408,72 +1408,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>642</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>2636</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>2,93%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>12,01%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>1185</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>3600</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>3720</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>10,67%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="O10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>32,4%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>642</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>3255</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>2,93%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>14,83%</t>
+          <t>33,48%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>519</t>
+          <t>506</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>4530</t>
+          <t>4491</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1503,12 +1503,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>13,7%</t>
+          <t>13,58%</t>
         </is>
       </c>
     </row>
@@ -1521,74 +1521,74 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>21310</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>19316</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>21952</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>97,07%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>87,99%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>15</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>9925</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>7510</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>7390</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
         <is>
           <t>11110</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>89,33%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>67,6%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>66,52%</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>21310</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>18697</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>21952</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>97,07%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>85,17%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
           <t>46</t>
@@ -1601,12 +1601,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>28532</t>
+          <t>28571</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>32543</t>
+          <t>32556</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1616,12 +1616,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>86,3%</t>
+          <t>86,42%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,43%</t>
+          <t>98,47%</t>
         </is>
       </c>
     </row>
@@ -1634,57 +1634,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>21952</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>21952</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>21952</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>17</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>11110</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>11110</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>11110</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>21952</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>21952</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>21952</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1756,102 +1756,102 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
+          <t>650</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>3229</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>1,68%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>8,33%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
           <t>793</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>3946</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>4457</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>2,1%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>10,47%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>650</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>11,83%</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>1443</t>
+        </is>
+      </c>
+      <c r="S13" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>3263</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>1,68%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>4504</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>1,89%</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>8,41%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>1443</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>4403</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>1,89%</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,76%</t>
+          <t>5,89%</t>
         </is>
       </c>
     </row>
@@ -1864,74 +1864,74 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>38139</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>35560</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>38789</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>98,32%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>91,67%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>55</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>36892</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>33739</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>33228</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
         <is>
           <t>37685</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>97,9%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>89,53%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>88,17%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>57</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>38139</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>35526</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>38789</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>98,32%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>91,59%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
           <t>112</t>
@@ -1944,7 +1944,7 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>72072</t>
+          <t>71971</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
@@ -1959,7 +1959,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>94,24%</t>
+          <t>94,11%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -1977,57 +1977,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>38789</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>38789</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>38789</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>56</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>37685</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>37685</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>37685</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>58</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>38789</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>38789</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>38789</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2094,72 +2094,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>1641</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>505</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>4534</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>504</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>4070</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>8,7%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>2,68%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>24,05%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>2,67%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>21,59%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2174,12 +2174,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>516</t>
+          <t>513</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>4484</t>
+          <t>4647</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2189,12 +2189,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>10,49%</t>
+          <t>10,87%</t>
         </is>
       </c>
     </row>
@@ -2207,72 +2207,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>23899</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>25</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>17212</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>14319</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>18348</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>14783</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>18349</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>91,3%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>75,95%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>97,32%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>23899</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>78,41%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>97,33%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2287,12 +2287,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>38268</t>
+          <t>38105</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>42236</t>
+          <t>42239</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2302,12 +2302,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>89,51%</t>
+          <t>89,13%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,79%</t>
+          <t>98,8%</t>
         </is>
       </c>
     </row>
@@ -2320,57 +2320,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>23899</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>23899</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>23899</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>28</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>18853</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>18853</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>18853</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>23899</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>23899</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>23899</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2550,47 +2550,47 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>11337</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>11</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
         <is>
           <t>7484</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>11337</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
@@ -2663,57 +2663,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>11337</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>11337</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>11337</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>11</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>7484</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="L21" s="2" t="inlineStr">
         <is>
           <t>7484</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="M21" s="2" t="inlineStr">
         <is>
           <t>7484</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>11337</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>11337</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>11337</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2780,72 +2780,72 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>3272</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>1294</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>7246</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>2,42%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>0,96%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>5,36%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>9</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="K22" s="2" t="inlineStr">
         <is>
           <t>5197</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>2596</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>9867</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>2792</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>9799</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
         <is>
           <t>4,74%</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>2,37%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>8,99%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>3272</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>1291</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>7172</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>2,42%</t>
-        </is>
-      </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>8,93%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2860,12 +2860,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>4441</t>
+          <t>4953</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>13527</t>
+          <t>13620</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2875,12 +2875,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>5,52%</t>
+          <t>5,56%</t>
         </is>
       </c>
     </row>
@@ -2893,72 +2893,72 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>197</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>132025</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>128051</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>134003</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>97,58%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>94,64%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>99,04%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>157</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="K23" s="2" t="inlineStr">
         <is>
           <t>104537</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>99867</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>107138</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>99935</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>106942</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
         <is>
           <t>95,26%</t>
         </is>
       </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>91,01%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>97,63%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>197</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>132025</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>128125</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>134006</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
-        <is>
-          <t>97,58%</t>
-        </is>
-      </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>94,7%</t>
+          <t>91,07%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>99,05%</t>
+          <t>97,46%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2973,12 +2973,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>231503</t>
+          <t>231410</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>240589</t>
+          <t>240077</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2988,12 +2988,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>94,48%</t>
+          <t>94,44%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>98,19%</t>
+          <t>97,98%</t>
         </is>
       </c>
     </row>
@@ -3006,57 +3006,57 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>202</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>135297</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>135297</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>135297</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>166</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="K24" s="2" t="inlineStr">
         <is>
           <t>109734</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
+      <c r="L24" s="2" t="inlineStr">
         <is>
           <t>109734</t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr">
+      <c r="M24" s="2" t="inlineStr">
         <is>
           <t>109734</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>202</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>135297</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>135297</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>135297</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3178,7 +3178,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -3189,7 +3189,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -3470,47 +3470,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>24953</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>38</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>26803</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>24953</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
@@ -3583,57 +3583,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>24953</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>24953</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>24953</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>38</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>26803</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>26803</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>26803</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>24953</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>24953</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>24953</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3700,107 +3700,107 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>787</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>3807</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>3836</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>3,07%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>14,86%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>14,97%</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R7" s="2" t="inlineStr">
+        <is>
+          <t>787</t>
+        </is>
+      </c>
+      <c r="S7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>3934</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
+          <t>1,94%</t>
+        </is>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>787</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>3873</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>1,94%</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>9,56%</t>
+          <t>9,71%</t>
         </is>
       </c>
     </row>
@@ -3813,74 +3813,74 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>14901</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>37</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>24832</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>21812</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>21783</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
         <is>
           <t>25619</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>96,93%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>85,14%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>85,03%</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>14901</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
           <t>59</t>
@@ -3893,7 +3893,7 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>36647</t>
+          <t>36586</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
@@ -3908,7 +3908,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>90,44%</t>
+          <t>90,29%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -3926,57 +3926,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>14901</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>14901</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>14901</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>38</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>25619</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>25619</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>25619</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>14901</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>14901</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>14901</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4048,102 +4048,102 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
+          <t>672</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>3604</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>3,69%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>19,78%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
           <t>627</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>3004</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>2766</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>3,93%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="O10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>18,82%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>672</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>17,33%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>1299</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>3661</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>3,69%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>4249</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>3,8%</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>20,09%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>1299</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>4560</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>3,8%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>13,34%</t>
+          <t>12,43%</t>
         </is>
       </c>
     </row>
@@ -4156,74 +4156,74 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>17551</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>14619</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>18223</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>96,31%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>80,22%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>22</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>15334</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>12957</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>13195</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
         <is>
           <t>15961</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>96,07%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>81,18%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>82,67%</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>17551</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>14562</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>18223</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>96,31%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>79,91%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
           <t>48</t>
@@ -4236,7 +4236,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>29624</t>
+          <t>29935</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -4251,7 +4251,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>86,66%</t>
+          <t>87,57%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -4269,57 +4269,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>18223</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>18223</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>18223</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>23</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>15961</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>15961</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>15961</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>18223</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>18223</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>18223</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4386,72 +4386,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>1620</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>5834</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>2,23%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>8,02%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>2087</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>502</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>6079</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>494</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>5463</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>3,45%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>0,83%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>10,05%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>1620</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>5658</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>2,23%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>7,78%</t>
+          <t>9,03%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4466,12 +4466,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1201</t>
+          <t>1288</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>8388</t>
+          <t>8188</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4481,12 +4481,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>6,15%</t>
         </is>
       </c>
     </row>
@@ -4499,72 +4499,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>71133</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>66919</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>72753</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>97,77%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>91,98%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>85</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>58390</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>54398</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>59975</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>55014</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>59983</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>96,55%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>89,95%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>99,17%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>99</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>71133</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>67095</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>72753</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>97,77%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>92,22%</t>
+          <t>90,97%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>99,18%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4579,12 +4579,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>124843</t>
+          <t>125043</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>132030</t>
+          <t>131943</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4594,12 +4594,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>93,7%</t>
+          <t>93,85%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,1%</t>
+          <t>99,03%</t>
         </is>
       </c>
     </row>
@@ -4612,57 +4612,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>101</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>72753</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>72753</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>72753</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>88</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>60477</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>60477</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>60477</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>101</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>72753</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>72753</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>72753</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -4729,107 +4729,107 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>647</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>3054</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>1,92%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>9,08%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="M16" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
+      <c r="O16" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I16" s="2" t="inlineStr">
+      <c r="P16" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J16" s="2" t="inlineStr">
+      <c r="Q16" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K16" s="2" t="inlineStr">
+      <c r="R16" s="2" t="inlineStr">
         <is>
           <t>647</t>
         </is>
       </c>
-      <c r="L16" s="2" t="inlineStr">
+      <c r="S16" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>2951</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>1,92%</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>3747</t>
+        </is>
+      </c>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
+          <t>0,91%</t>
+        </is>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>8,78%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>647</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>3247</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>0,91%</t>
-        </is>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>5,26%</t>
         </is>
       </c>
     </row>
@@ -4842,74 +4842,74 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>32983</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>30576</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>33630</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>98,08%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>90,92%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>53</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>37598</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
+      <c r="M17" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
+      <c r="O17" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I17" s="2" t="inlineStr">
+      <c r="P17" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>46</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>32983</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>30679</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>33630</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>98,08%</t>
-        </is>
-      </c>
-      <c r="O17" s="2" t="inlineStr">
-        <is>
-          <t>91,22%</t>
-        </is>
-      </c>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q17" s="2" t="inlineStr">
         <is>
           <t>99</t>
@@ -4922,7 +4922,7 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>67982</t>
+          <t>67482</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
@@ -4937,7 +4937,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>95,44%</t>
+          <t>94,74%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -4955,57 +4955,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>33630</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>33630</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>33630</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>53</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>37598</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>37598</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>37598</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>47</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>33630</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>33630</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>33630</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -5072,92 +5072,92 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>2644</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>5592</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>18,26%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>4,49%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>38,63%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="K19" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="L19" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="M19" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="N19" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
+      <c r="O19" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I19" s="2" t="inlineStr">
+      <c r="P19" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J19" s="2" t="inlineStr">
+      <c r="Q19" s="2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="K19" s="2" t="inlineStr">
+      <c r="R19" s="2" t="inlineStr">
         <is>
           <t>2644</t>
         </is>
       </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>640</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>5432</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>18,26%</t>
-        </is>
-      </c>
-      <c r="O19" s="2" t="inlineStr">
-        <is>
-          <t>4,42%</t>
-        </is>
-      </c>
-      <c r="P19" s="2" t="inlineStr">
-        <is>
-          <t>37,52%</t>
-        </is>
-      </c>
-      <c r="Q19" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="R19" s="2" t="inlineStr">
-        <is>
-          <t>2644</t>
-        </is>
-      </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>729</t>
+          <t>655</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>6585</t>
+          <t>6117</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5167,12 +5167,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>25,07%</t>
+          <t>23,29%</t>
         </is>
       </c>
     </row>
@@ -5190,69 +5190,69 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
+          <t>11832</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>8884</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>13827</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>81,74%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>61,37%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>95,51%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
           <t>11795</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="L20" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
+      <c r="M20" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="N20" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
+      <c r="O20" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I20" s="2" t="inlineStr">
+      <c r="P20" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>11832</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>9044</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>13836</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>81,74%</t>
-        </is>
-      </c>
-      <c r="O20" s="2" t="inlineStr">
-        <is>
-          <t>62,48%</t>
-        </is>
-      </c>
-      <c r="P20" s="2" t="inlineStr">
-        <is>
-          <t>95,58%</t>
-        </is>
-      </c>
       <c r="Q20" s="2" t="inlineStr">
         <is>
           <t>34</t>
@@ -5265,12 +5265,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>19686</t>
+          <t>20154</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>25542</t>
+          <t>25616</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5280,12 +5280,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>74,93%</t>
+          <t>76,71%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>97,22%</t>
+          <t>97,51%</t>
         </is>
       </c>
     </row>
@@ -5298,57 +5298,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>14476</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>14476</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>14476</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>17</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>11795</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="L21" s="2" t="inlineStr">
         <is>
           <t>11795</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="M21" s="2" t="inlineStr">
         <is>
           <t>11795</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>14476</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>14476</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>14476</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -5415,72 +5415,72 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>5582</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>2601</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>10773</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>3,12%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>1,45%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>6,02%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="K22" s="2" t="inlineStr">
         <is>
           <t>3501</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>1123</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>7630</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>1219</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>8199</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
         <is>
           <t>1,96%</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>0,63%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>4,28%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>5582</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>2544</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>10814</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>3,12%</t>
-        </is>
-      </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>6,04%</t>
+          <t>4,6%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5495,12 +5495,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>4958</t>
+          <t>5133</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>14855</t>
+          <t>15481</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5510,12 +5510,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>4,33%</t>
         </is>
       </c>
     </row>
@@ -5528,72 +5528,72 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>245</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>173354</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>168163</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>176335</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>96,88%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>93,98%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>98,55%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>252</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="K23" s="2" t="inlineStr">
         <is>
           <t>174753</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>170624</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>177131</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>170055</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>177035</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
         <is>
           <t>98,04%</t>
         </is>
       </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>95,72%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>99,37%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>245</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>173354</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>168122</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>176392</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
-        <is>
-          <t>96,88%</t>
-        </is>
-      </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>93,96%</t>
+          <t>95,4%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>98,58%</t>
+          <t>99,32%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5608,12 +5608,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>342335</t>
+          <t>341709</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>352232</t>
+          <t>352057</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5623,12 +5623,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>95,84%</t>
+          <t>95,67%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>98,61%</t>
+          <t>98,56%</t>
         </is>
       </c>
     </row>
@@ -5641,57 +5641,57 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>253</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>178936</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>178936</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>178936</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>257</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="K24" s="2" t="inlineStr">
         <is>
           <t>178254</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
+      <c r="L24" s="2" t="inlineStr">
         <is>
           <t>178254</t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr">
+      <c r="M24" s="2" t="inlineStr">
         <is>
           <t>178254</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>253</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>178936</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>178936</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>178936</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -5813,7 +5813,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -5824,7 +5824,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -6105,47 +6105,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>21028</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>28</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>18999</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>21028</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
@@ -6218,57 +6218,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>21028</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>21028</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>21028</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>28</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>18999</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>18999</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>18999</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>21028</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>21028</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>21028</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6340,67 +6340,67 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
+          <t>1399</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>4287</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>6,29%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>19,26%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
           <t>1153</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>3528</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>3522</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>5,73%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>17,53%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>1399</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>4792</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>6,29%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>21,53%</t>
+          <t>17,5%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6415,12 +6415,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>701</t>
+          <t>678</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>5835</t>
+          <t>5840</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6430,12 +6430,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>13,77%</t>
+          <t>13,78%</t>
         </is>
       </c>
     </row>
@@ -6448,74 +6448,74 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>20862</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>17974</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>22261</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>93,71%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>80,74%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>28</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>18977</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>16602</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>16608</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
         <is>
           <t>20130</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>94,27%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>82,47%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>82,5%</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>20862</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>17469</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>22261</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>93,71%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>78,47%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
           <t>59</t>
@@ -6528,12 +6528,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>36555</t>
+          <t>36550</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>41689</t>
+          <t>41712</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6543,12 +6543,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>86,23%</t>
+          <t>86,22%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,35%</t>
+          <t>98,4%</t>
         </is>
       </c>
     </row>
@@ -6561,57 +6561,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>22261</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>22261</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>22261</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>30</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>20130</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>20130</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>20130</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>22261</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>22261</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>22261</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6678,107 +6678,107 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>700</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>3027</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>5,94%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>25,7%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="M10" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="O10" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
+      <c r="P10" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J10" s="2" t="inlineStr">
+      <c r="Q10" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K10" s="2" t="inlineStr">
+      <c r="R10" s="2" t="inlineStr">
         <is>
           <t>700</t>
         </is>
       </c>
-      <c r="L10" s="2" t="inlineStr">
+      <c r="S10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>3474</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>5,94%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>3591</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>2,96%</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>29,5%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>700</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>3540</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>2,96%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>14,96%</t>
+          <t>15,18%</t>
         </is>
       </c>
     </row>
@@ -6791,74 +6791,74 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>11078</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>8751</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>11778</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>94,06%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>74,3%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>18</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>11883</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="M11" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
+      <c r="O11" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="P11" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>11078</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>8304</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>11778</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>94,06%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>70,5%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
           <t>35</t>
@@ -6871,7 +6871,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>20121</t>
+          <t>20070</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -6886,7 +6886,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>85,04%</t>
+          <t>84,82%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -6909,52 +6909,52 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
+          <t>11778</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>11778</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>11778</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
           <t>11883</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>11883</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>11883</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>11778</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>11778</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>11778</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7021,72 +7021,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>700</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>3425</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>1,63%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>7,96%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>1124</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>4155</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>3453</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>1,99%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>7,35%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>700</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>3552</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>1,63%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>8,26%</t>
+          <t>6,1%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7101,12 +7101,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>552</t>
+          <t>548</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>4985</t>
+          <t>5009</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7121,7 +7121,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>5,03%</t>
         </is>
       </c>
     </row>
@@ -7134,74 +7134,74 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>42297</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>39572</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>42997</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>98,37%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>92,04%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>86</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>55437</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>52406</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>53108</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
         <is>
           <t>56561</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>98,01%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>92,65%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>93,9%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>62</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>42297</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>39445</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>42997</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>98,37%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>91,74%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
           <t>148</t>
@@ -7214,12 +7214,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>94573</t>
+          <t>94549</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>99006</t>
+          <t>99010</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7229,7 +7229,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>94,99%</t>
+          <t>94,97%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -7247,57 +7247,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>42997</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>42997</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>42997</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>88</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>56561</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>56561</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>56561</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>63</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>42997</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>42997</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>42997</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7477,47 +7477,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>30245</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>53</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>35779</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>30245</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
@@ -7590,57 +7590,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>30245</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>30245</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>30245</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>53</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>35779</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>35779</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>35779</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>30245</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>30245</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>30245</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -7820,47 +7820,47 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>12086</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>19</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
         <is>
           <t>13025</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>12086</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
@@ -7933,57 +7933,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>12086</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>12086</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>12086</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>19</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>13025</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="L21" s="2" t="inlineStr">
         <is>
           <t>13025</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="M21" s="2" t="inlineStr">
         <is>
           <t>13025</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>12086</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>12086</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>12086</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -8055,67 +8055,67 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
+          <t>2799</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>705</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>6968</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>1,99%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>0,5%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>4,96%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
           <t>2277</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>601</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>5367</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>572</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>5307</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
         <is>
           <t>1,46%</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>0,38%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>3,43%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>2799</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>703</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>7029</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>1,99%</t>
-        </is>
-      </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>3,39%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8130,12 +8130,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>2463</t>
+          <t>2189</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>9645</t>
+          <t>9194</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8145,12 +8145,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>3,1%</t>
         </is>
       </c>
     </row>
@@ -8163,72 +8163,72 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>137595</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>133426</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>139689</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>98,01%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>95,04%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>99,5%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>232</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="K23" s="2" t="inlineStr">
         <is>
           <t>154100</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>151010</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>155776</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>151070</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>155805</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
         <is>
           <t>98,54%</t>
         </is>
       </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>96,57%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>99,62%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>137595</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>133365</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>139691</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
-        <is>
-          <t>98,01%</t>
-        </is>
-      </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>94,99%</t>
+          <t>96,61%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>99,5%</t>
+          <t>99,63%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8243,12 +8243,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>287125</t>
+          <t>287576</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>294307</t>
+          <t>294581</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8258,12 +8258,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>96,75%</t>
+          <t>96,9%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>99,17%</t>
+          <t>99,26%</t>
         </is>
       </c>
     </row>
@@ -8276,57 +8276,57 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>204</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>140394</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>140394</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>140394</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>236</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="K24" s="2" t="inlineStr">
         <is>
           <t>156377</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
+      <c r="L24" s="2" t="inlineStr">
         <is>
           <t>156377</t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr">
+      <c r="M24" s="2" t="inlineStr">
         <is>
           <t>156377</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>204</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>140394</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>140394</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>140394</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
